--- a/data-raw/indices/mode-strategy-interactions.xlsx
+++ b/data-raw/indices/mode-strategy-interactions.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10111"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rotenle/Documents/MetC_Locals/CD/ghg.sp/data-raw/indices/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D12D7E-638E-784A-B5FA-28177B2CAF71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36BFAD72-1D1D-2A49-B260-5B73D41117F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2140" yWindow="1600" windowWidth="27240" windowHeight="15940" xr2:uid="{74981066-E890-3447-856A-8829176FD2DF}"/>
+    <workbookView xWindow="1880" yWindow="1580" windowWidth="27240" windowHeight="15940" xr2:uid="{74981066-E890-3447-856A-8829176FD2DF}"/>
   </bookViews>
   <sheets>
     <sheet name="Passenger" sheetId="1" r:id="rId1"/>
@@ -34,14 +34,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="25">
   <si>
     <t>Intervention</t>
   </si>
   <si>
-    <t>BRT</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -60,9 +57,6 @@
     <t>Transit ridership (increase)</t>
   </si>
   <si>
-    <t>Average vehicle occupancy (increase)</t>
-  </si>
-  <si>
     <t>LU - Diversity/Entropy (increase)</t>
   </si>
   <si>
@@ -75,27 +69,12 @@
     <t>LU - Job accessability via transit (increase)</t>
   </si>
   <si>
-    <t>School bus</t>
-  </si>
-  <si>
     <t>Passenger LDV</t>
   </si>
   <si>
     <t>Walk/Bike</t>
   </si>
   <si>
-    <t>Bus</t>
-  </si>
-  <si>
-    <t>Rail urban</t>
-  </si>
-  <si>
-    <t>Rail intercity</t>
-  </si>
-  <si>
-    <t>Autonomous veh</t>
-  </si>
-  <si>
     <t>Vehicle ownership costs (increase)</t>
   </si>
   <si>
@@ -118,6 +97,18 @@
   </si>
   <si>
     <t>increases VMT</t>
+  </si>
+  <si>
+    <t>Transit</t>
+  </si>
+  <si>
+    <t>same function as VMT fee</t>
+  </si>
+  <si>
+    <t>Transit average vehicle occupancy (increase)</t>
+  </si>
+  <si>
+    <t>increase AVO decreases PMT</t>
   </si>
 </sst>
 </file>
@@ -478,384 +469,231 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B215526-DA24-6D42-9CC5-8EA4EE40C873}">
-  <dimension ref="A2:J18"/>
+  <dimension ref="A2:E17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="36.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.1640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.1640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="5.33203125" customWidth="1"/>
-    <col min="6" max="6" width="9.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.83203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C2" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
-        <v>1</v>
-      </c>
-      <c r="F2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-      <c r="H2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I2" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>3</v>
-      </c>
-      <c r="D3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" t="s">
-        <v>3</v>
-      </c>
-      <c r="F3" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" t="s">
-        <v>3</v>
-      </c>
-      <c r="I3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" t="s">
-        <v>5</v>
       </c>
       <c r="B4">
         <v>0</v>
       </c>
       <c r="C4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
-        <v>3</v>
-      </c>
-      <c r="G4" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" t="s">
+        <v>2</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>10</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" t="s">
-        <v>3</v>
-      </c>
-      <c r="E5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F5" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" t="s">
-        <v>3</v>
-      </c>
-      <c r="D6" t="s">
-        <v>3</v>
-      </c>
-      <c r="E6" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" t="s">
-        <v>3</v>
-      </c>
-      <c r="G6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C7" t="s">
-        <v>2</v>
-      </c>
-      <c r="D7" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" t="s">
-        <v>3</v>
-      </c>
-      <c r="F7" t="s">
-        <v>3</v>
-      </c>
-      <c r="G7" t="s">
-        <v>3</v>
-      </c>
-      <c r="I7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" t="s">
-        <v>11</v>
-      </c>
-      <c r="B8" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D8" t="s">
-        <v>2</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2</v>
-      </c>
-      <c r="F8" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2</v>
-      </c>
-      <c r="I8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A9" t="s">
-        <v>12</v>
-      </c>
-      <c r="B9" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E9" t="s">
-        <v>3</v>
-      </c>
-      <c r="F9" t="s">
-        <v>3</v>
-      </c>
-      <c r="G9" t="s">
-        <v>3</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A11" t="s">
-        <v>8</v>
-      </c>
-      <c r="I11" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="B12" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D12" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>2</v>
-      </c>
-      <c r="F12" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" t="s">
-        <v>2</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D13" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>2</v>
-      </c>
-      <c r="F13" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" t="s">
-        <v>2</v>
-      </c>
-      <c r="H13" t="s">
-        <v>2</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C14" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D14" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" t="s">
-        <v>3</v>
-      </c>
-      <c r="G14" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2</v>
+      </c>
+      <c r="E15" t="s">
         <v>22</v>
       </c>
-      <c r="B15" t="s">
-        <v>2</v>
-      </c>
-      <c r="I15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>2</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D17" t="s">
-        <v>3</v>
-      </c>
-      <c r="E17" t="s">
-        <v>3</v>
-      </c>
-      <c r="F17" t="s">
-        <v>3</v>
-      </c>
-      <c r="G17" t="s">
-        <v>3</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="I18">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/data-raw/indices/mode-strategy-interactions.xlsx
+++ b/data-raw/indices/mode-strategy-interactions.xlsx
@@ -699,4 +699,201 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100955DD26AA61AEC438713239C5D34F7C5" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5f64bad1cc293dc5faccbf42e240b9dd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="735c679e-a73a-4d40-ac37-586f07e9723a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="22e8c6e311a9f235a237b96f8afc2b5e" ns2:_="">
+    <xsd:import namespace="735c679e-a73a-4d40-ac37-586f07e9723a"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="735c679e-a73a-4d40-ac37-586f07e9723a" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="10" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="11" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="12" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="13" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="14" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9906AFFE-446E-4529-BC48-533AA192CF26}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FDF3B972-C5C9-41CF-8F0B-256A283155B3}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74EB2D00-D32C-44A3-83E1-5A0965B8B202}"/>
 </file>
--- a/data-raw/indices/mode-strategy-interactions.xlsx
+++ b/data-raw/indices/mode-strategy-interactions.xlsx
@@ -702,9 +702,10 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100955DD26AA61AEC438713239C5D34F7C5" ma:contentTypeVersion="8" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="5f64bad1cc293dc5faccbf42e240b9dd">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="735c679e-a73a-4d40-ac37-586f07e9723a" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="22e8c6e311a9f235a237b96f8afc2b5e" ns2:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100955DD26AA61AEC438713239C5D34F7C5" ma:contentTypeVersion="10" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="46f9bf9fee5e07c8f3aafb1030afb21d">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="735c679e-a73a-4d40-ac37-586f07e9723a" xmlns:ns3="97f38cb2-3311-4671-91cc-d9fdb7cb0538" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="5a7dabcb4ca83edae4be666ebc7f32e4" ns2:_="" ns3:_="">
     <xsd:import namespace="735c679e-a73a-4d40-ac37-586f07e9723a"/>
+    <xsd:import namespace="97f38cb2-3311-4671-91cc-d9fdb7cb0538"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -719,6 +720,8 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -769,6 +772,36 @@
     <xsd:element name="MediaServiceEventHashCode" ma:index="15" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="97f38cb2-3311-4671-91cc-d9fdb7cb0538" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="16" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="17" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -887,7 +920,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9906AFFE-446E-4529-BC48-533AA192CF26}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0AEC5687-2BAF-4160-94F6-46C0D950BEEB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
